--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -5346,7 +5346,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251111_201516.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
